--- a/.venv/Lib/QandA.xlsx
+++ b/.venv/Lib/QandA.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2943"/>
+  <dimension ref="A1:I3000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="39.77734375" customWidth="1" min="1" max="1"/>
@@ -42592,6 +42592,770 @@
       <c r="F2943" t="inlineStr">
         <is>
           <t>危化品建设项目竣工投入生产或者使用前，安全设施未经验收合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="2944">
+      <c r="A2944" t="inlineStr">
+        <is>
+          <t>申请危险化学品安全使用许可证的化工企业，无需具备以下哪个条件（）</t>
+        </is>
+      </c>
+      <c r="B2944" t="inlineStr">
+        <is>
+          <t>为从业人员购买商业意外险</t>
+        </is>
+      </c>
+    </row>
+    <row r="2945">
+      <c r="A2945" t="inlineStr">
+        <is>
+          <t>金山区上海某科技贸易有限公司因进口危险化学品未办理登记被处罚，最终罚款金额为（）</t>
+        </is>
+      </c>
+      <c r="B2945" t="inlineStr">
+        <is>
+          <t>1.5万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="2946">
+      <c r="A2946" t="inlineStr">
+        <is>
+          <t>危险化学品登记信息无需与以下哪个单位共享（）</t>
+        </is>
+      </c>
+      <c r="B2946" t="inlineStr">
+        <is>
+          <t>行业协会</t>
+        </is>
+      </c>
+    </row>
+    <row r="2947">
+      <c r="A2947" t="inlineStr">
+        <is>
+          <t>危险化学品登记的主体不包括以下哪类（）</t>
+        </is>
+      </c>
+      <c r="B2947" t="inlineStr">
+        <is>
+          <t>危险化学品使用企业</t>
+        </is>
+      </c>
+    </row>
+    <row r="2948">
+      <c r="A2948" t="inlineStr">
+        <is>
+          <t>对同一企业生产、进口的同一品种的危险化学品，需要进行重复登记。（）</t>
+        </is>
+      </c>
+      <c r="B2948" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="2949">
+      <c r="A2949" t="inlineStr">
+        <is>
+          <t>危险化学品生产企业办理登记的时间要求为（ ）</t>
+        </is>
+      </c>
+      <c r="B2949" t="inlineStr">
+        <is>
+          <t>竣工验收前办理</t>
+        </is>
+      </c>
+    </row>
+    <row r="2950">
+      <c r="A2950" t="inlineStr">
+        <is>
+          <t>化学品的危险特性尚未确定的，任何单位和个人不得擅自从事该化学品的生产、储存等活动。</t>
+        </is>
+      </c>
+      <c r="B2950" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2951">
+      <c r="A2951" t="inlineStr">
+        <is>
+          <t>研究开发、试产试销过程中的低量低释放、低暴露的危险化学品，国家免予登记。</t>
+        </is>
+      </c>
+      <c r="B2951" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2952">
+      <c r="A2952" t="inlineStr">
+        <is>
+          <t>研究开发、试产试销过程中的低量低释放、低暴露的危险化学品，国家免予登记。（）</t>
+        </is>
+      </c>
+      <c r="B2952" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2953">
+      <c r="A2953" t="inlineStr">
+        <is>
+          <t>剧毒、易制爆化学品的销售、购买后，应在几日内向公安机关备案</t>
+        </is>
+      </c>
+      <c r="B2953" t="inlineStr">
+        <is>
+          <t>3日内</t>
+        </is>
+      </c>
+    </row>
+    <row r="2954">
+      <c r="A2954" t="inlineStr">
+        <is>
+          <t>购买剧毒化学品的单位，应向哪个部门申请购买许可证（）</t>
+        </is>
+      </c>
+      <c r="B2954" t="inlineStr">
+        <is>
+          <t>公安机关</t>
+        </is>
+      </c>
+    </row>
+    <row r="2955">
+      <c r="A2955" t="inlineStr">
+        <is>
+          <t>国家对危险化学品经营实行什么制度（）</t>
+        </is>
+      </c>
+      <c r="B2955" t="inlineStr">
+        <is>
+          <t>许可制度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2956">
+      <c r="A2956" t="inlineStr">
+        <is>
+          <t>从事危化品经营的企业，从业人员无需培训考核即可上岗。</t>
+        </is>
+      </c>
+      <c r="B2956" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="2957">
+      <c r="A2957" t="inlineStr">
+        <is>
+          <t>危险化学品经营包括仓储经营，二者均需遵守经营安全相关规定。</t>
+        </is>
+      </c>
+      <c r="B2957" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2958">
+      <c r="A2958" t="inlineStr">
+        <is>
+          <t>剧毒、易制爆化学品的销售、购买后,应在几日内向公安机关备案</t>
+        </is>
+      </c>
+      <c r="B2958" t="inlineStr">
+        <is>
+          <t>3日内</t>
+        </is>
+      </c>
+    </row>
+    <row r="2959">
+      <c r="A2959" t="inlineStr">
+        <is>
+          <t>从事剧毒化学品经营的企业,应向哪个层级应急管理部门提出申请（）</t>
+        </is>
+      </c>
+      <c r="B2959" t="inlineStr">
+        <is>
+          <t>市级</t>
+        </is>
+      </c>
+    </row>
+    <row r="2960">
+      <c r="A2960" t="inlineStr">
+        <is>
+          <t>危化品经营许可仅分为带仓储经营一种类型。</t>
+        </is>
+      </c>
+      <c r="B2960" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="2961">
+      <c r="A2961" t="inlineStr">
+        <is>
+          <t>从事危化品经营的企业,从业人员无需培训考核即可上岗。</t>
+        </is>
+      </c>
+      <c r="B2961" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="2962">
+      <c r="A2962" t="inlineStr">
+        <is>
+          <t>危险化学品商店内只能存放哪种类型的危险化学品（）</t>
+        </is>
+      </c>
+      <c r="B2962" t="inlineStr">
+        <is>
+          <t>民用小包装</t>
+        </is>
+      </c>
+    </row>
+    <row r="2963">
+      <c r="A2963" t="inlineStr">
+        <is>
+          <t>未取得危险化学品经营许可证从事经营活动,应急管理部门可处的罚款金额为（）</t>
+        </is>
+      </c>
+      <c r="B2963" t="inlineStr">
+        <is>
+          <t>10万以上50万以下</t>
+        </is>
+      </c>
+    </row>
+    <row r="2964">
+      <c r="A2964" t="inlineStr">
+        <is>
+          <t>危化品经营企业的储存设施只需满足企业内部标准即可。</t>
+        </is>
+      </c>
+      <c r="B2964" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="2965">
+      <c r="A2965" t="inlineStr">
+        <is>
+          <t>申请人取得危化品经营许可证后,无需办理市场监管登记即可经营.</t>
+        </is>
+      </c>
+      <c r="B2965" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="2966">
+      <c r="A2966" t="inlineStr">
+        <is>
+          <t>购买剧毒化学品的单位,应向哪个部门申请购买许可证（）</t>
+        </is>
+      </c>
+      <c r="B2966" t="inlineStr">
+        <is>
+          <t>公安机关</t>
+        </is>
+      </c>
+    </row>
+    <row r="2967">
+      <c r="A2967" t="inlineStr">
+        <is>
+          <t>购买剧毒化学品的单位,应向哪个部门申请购买许可证()</t>
+        </is>
+      </c>
+      <c r="B2967" t="inlineStr">
+        <is>
+          <t>公安机关</t>
+        </is>
+      </c>
+    </row>
+    <row r="2968">
+      <c r="A2968" t="inlineStr">
+        <is>
+          <t>国家对危险化学品经营实行什么制度()</t>
+        </is>
+      </c>
+      <c r="B2968" t="inlineStr">
+        <is>
+          <t>许可制度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2969">
+      <c r="A2969" t="inlineStr">
+        <is>
+          <t>化学品安全技术说明书包含的信息部分数量为()</t>
+        </is>
+      </c>
+      <c r="B2969" t="inlineStr">
+        <is>
+          <t>16部分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2970">
+      <c r="A2970" t="inlineStr">
+        <is>
+          <t>危化品经营企业的储存设施只需满足企业内部标准即可.</t>
+        </is>
+      </c>
+      <c r="B2970" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="2971">
+      <c r="A2971" t="inlineStr">
+        <is>
+          <t>对重复使用的危险化学品包装物、容器,使用单位在重复使用前应当进行检查;发现存在安全隐患的,应当及时维修或者更换.</t>
+        </is>
+      </c>
+      <c r="B2971" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2972">
+      <c r="A2972" t="inlineStr">
+        <is>
+          <t>危险化学品包装物、容器的材质以及危险化学品包装的型式、规格、方法和单件质量,应当与所包装的危险化学品的性质和用途相适应.</t>
+        </is>
+      </c>
+      <c r="B2972" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2973">
+      <c r="A2973" t="inlineStr">
+        <is>
+          <t>依据《危险化学品安全法》,剧毒化学品以及储存数量构成重大危险源的其他危险化学品,应当在专用储存场所内单独存放,实行()制度,收发记录的保存期限不得少于三年.</t>
+        </is>
+      </c>
+      <c r="B2973" t="inlineStr">
+        <is>
+          <t>双人收发、双人保管</t>
+        </is>
+      </c>
+    </row>
+    <row r="2974">
+      <c r="A2974" t="inlineStr">
+        <is>
+          <t>依据《危险化学品安全法》,储存危险化学品的单位应当对其危险化学品专用储存场所的安全设施、设备定期进行().</t>
+        </is>
+      </c>
+      <c r="B2974" t="inlineStr">
+        <is>
+          <t>检测、检验</t>
+        </is>
+      </c>
+    </row>
+    <row r="2975">
+      <c r="A2975" t="inlineStr">
+        <is>
+          <t>下列哪些属于危险化学品专用储存场所?</t>
+        </is>
+      </c>
+      <c r="B2975" t="inlineStr">
+        <is>
+          <t>专用仓库</t>
+        </is>
+      </c>
+      <c r="C2975" t="inlineStr">
+        <is>
+          <t>专用场地</t>
+        </is>
+      </c>
+      <c r="D2975" t="inlineStr">
+        <is>
+          <t>专用储存室</t>
+        </is>
+      </c>
+      <c r="E2975" t="inlineStr">
+        <is>
+          <t>储存专柜</t>
+        </is>
+      </c>
+    </row>
+    <row r="2976">
+      <c r="A2976" t="inlineStr">
+        <is>
+          <t>危化品新工艺开发,可将未经中试的技术直接用于工业化生产.</t>
+        </is>
+      </c>
+      <c r="B2976" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="2977">
+      <c r="A2977" t="inlineStr">
+        <is>
+          <t>跨公司转岗的危化品从业人员,应重新接受完整的三级安全教育培训.</t>
+        </is>
+      </c>
+      <c r="B2977" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2978">
+      <c r="A2978" t="inlineStr">
+        <is>
+          <t>篡改安全监控设备相关数据,可能构成《刑法》中的危险作业罪.</t>
+        </is>
+      </c>
+      <c r="B2978" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2979">
+      <c r="A2979" t="inlineStr">
+        <is>
+          <t>危化品生产企业主要负责人自任职之日起()个月内,必须取得安全考核合格证书.</t>
+        </is>
+      </c>
+      <c r="B2979" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2980">
+      <c r="A2980" t="inlineStr">
+        <is>
+          <t>安全风险分级管控制度的适用企业包括()</t>
+        </is>
+      </c>
+      <c r="B2980" t="inlineStr">
+        <is>
+          <t>生产危化品的企业</t>
+        </is>
+      </c>
+      <c r="C2980" t="inlineStr">
+        <is>
+          <t>储存危化品的企业</t>
+        </is>
+      </c>
+      <c r="D2980" t="inlineStr">
+        <is>
+          <t>使用危化品从事生产的企业</t>
+        </is>
+      </c>
+    </row>
+    <row r="2981">
+      <c r="A2981" t="inlineStr">
+        <is>
+          <t>生产、储存危险化学品的企业不得使用国家明令淘汰或者禁止使用的危及生产安全的工艺、技术、设施、设备.</t>
+        </is>
+      </c>
+      <c r="B2981" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2982">
+      <c r="A2982" t="inlineStr">
+        <is>
+          <t>进行可能危及危险化学品管道安全的施工作业,施工单位应当在开工的()日前将施工方案书面通知管道所属单位,并与管道所属单位共同制定应急预案,采取相应的安全防护措施.</t>
+        </is>
+      </c>
+      <c r="B2982" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2983">
+      <c r="A2983" t="inlineStr">
+        <is>
+          <t>危化品企业应根据危化品的(),设置相应的安全设施.</t>
+        </is>
+      </c>
+      <c r="B2983" t="inlineStr">
+        <is>
+          <t>种类和危险特性</t>
+        </is>
+      </c>
+    </row>
+    <row r="2984">
+      <c r="A2984" t="inlineStr">
+        <is>
+          <t>生产、储存、使用危险化学品的企业,应当委托具备国家规定的资质条件的机构,对本企业的安全生产条件每三年进行一次安全评价,提出安全评价报告.</t>
+        </is>
+      </c>
+      <c r="B2984" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2985">
+      <c r="A2985" t="inlineStr">
+        <is>
+          <t>储存易制爆危化品的单位,可仅配备兼职治安保卫人员.</t>
+        </is>
+      </c>
+      <c r="B2985" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="2986">
+      <c r="A2986" t="inlineStr">
+        <is>
+          <t>生产、储存危险化学品的单位,对公共区域( )的危化品输送管道负有安全管理责任.</t>
+        </is>
+      </c>
+      <c r="B2986" t="inlineStr">
+        <is>
+          <t>埋地、地面和架空</t>
+        </is>
+      </c>
+    </row>
+    <row r="2987">
+      <c r="A2987" t="inlineStr">
+        <is>
+          <t>危化品企业安全风险监测预警系统应与()实现互联互通.</t>
+        </is>
+      </c>
+      <c r="B2987" t="inlineStr">
+        <is>
+          <t>政府有关部门</t>
+        </is>
+      </c>
+    </row>
+    <row r="2988">
+      <c r="A2988" t="inlineStr">
+        <is>
+          <t>根据《危险化学品安全法》,危险化学品建设项目的安全设施投资应当().</t>
+        </is>
+      </c>
+      <c r="B2988" t="inlineStr">
+        <is>
+          <t>纳入建设项目概算</t>
+        </is>
+      </c>
+    </row>
+    <row r="2989">
+      <c r="A2989" t="inlineStr">
+        <is>
+          <t>根据《危险化学品安全法》,危险化学品建设项目应当由()进行安全条件审查.</t>
+        </is>
+      </c>
+      <c r="B2989" t="inlineStr">
+        <is>
+          <t>应急管理部门</t>
+        </is>
+      </c>
+    </row>
+    <row r="2990">
+      <c r="A2990" t="inlineStr">
+        <is>
+          <t>()、()危险化学品生产建设项目应当进入化工园区,与其他行业生产装置配套建设的项目和符合国家规定的其他项目除外.除为化工企业提供配套服务的企业外,非化工企业禁止进入化工园区.</t>
+        </is>
+      </c>
+      <c r="B2990" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="C2990" t="inlineStr">
+        <is>
+          <t>扩建</t>
+        </is>
+      </c>
+    </row>
+    <row r="2991">
+      <c r="A2991" t="inlineStr">
+        <is>
+          <t>下列情形中,负有危险化学品安全监督管理职责的部门可责令停止建设或者停产停业整顿、限期改正,并对建设单位处10万元以上50万元以下罚款的有()</t>
+        </is>
+      </c>
+      <c r="B2991" t="inlineStr">
+        <is>
+          <t>危化品建设项目未经安全条件审查擅自开工</t>
+        </is>
+      </c>
+      <c r="C2991" t="inlineStr">
+        <is>
+          <t>危化品建设项目没有安全设施设计即开工建设</t>
+        </is>
+      </c>
+      <c r="D2991" t="inlineStr">
+        <is>
+          <t>施工单位未按照批准的安全设施设计施工</t>
+        </is>
+      </c>
+      <c r="E2991" t="inlineStr">
+        <is>
+          <t>实行工程监理的危化品建设项目,建设单位未委托监理单位对安全设施施工监理</t>
+        </is>
+      </c>
+      <c r="F2991" t="inlineStr">
+        <is>
+          <t>危化品建设项目竣工投入生产或者使用前,安全设施未经验收合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="2992">
+      <c r="A2992" t="inlineStr">
+        <is>
+          <t>施工单位必须按照批准的安全设施设计施工,并对安全设施的工程质量和施工安全负责.</t>
+        </is>
+      </c>
+      <c r="B2992" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="A2993" t="inlineStr">
+        <is>
+          <t>危险化学品建设项目的安全设施设计,应当报所在地()以上人民政府应急管理部门审查.</t>
+        </is>
+      </c>
+      <c r="B2993" t="inlineStr">
+        <is>
+          <t>设区的市级</t>
+        </is>
+      </c>
+    </row>
+    <row r="2994">
+      <c r="A2994" t="inlineStr">
+        <is>
+          <t>化工园区应当对进出园区的所有危险化学品实行动态监管,对园区内企业、重点场所、重大危险源、基础设施实施风险监测预警.</t>
+        </is>
+      </c>
+      <c r="B2994" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="2995">
+      <c r="A2995" t="inlineStr">
+        <is>
+          <t>以下哪种化学品不属于危险化学品范畴.()</t>
+        </is>
+      </c>
+      <c r="B2995" t="inlineStr">
+        <is>
+          <t>硫酸铵</t>
+        </is>
+      </c>
+    </row>
+    <row r="2996">
+      <c r="A2996" t="inlineStr">
+        <is>
+          <t>依据《特种作业人员安全技术培训考核管理规定》,下列不属于特种作业的是().</t>
+        </is>
+      </c>
+      <c r="B2996" t="inlineStr">
+        <is>
+          <t>机械作业</t>
+        </is>
+      </c>
+    </row>
+    <row r="2997">
+      <c r="A2997" t="inlineStr">
+        <is>
+          <t>根据《危险化学品重大危险源辨识》,当计算出的R值为1.8时,该重大危险源的级别为()</t>
+        </is>
+      </c>
+      <c r="B2997" t="inlineStr">
+        <is>
+          <t>四级</t>
+        </is>
+      </c>
+    </row>
+    <row r="2998">
+      <c r="A2998" t="inlineStr">
+        <is>
+          <t>危险化学品安全管理工作实行()、()、(),强化和落实单位主体责任与政府监管责任,建立单位负责职工参与、政府监管、行业自律、社会监督的机制.</t>
+        </is>
+      </c>
+      <c r="B2998" t="inlineStr">
+        <is>
+          <t>管行业必须管安全</t>
+        </is>
+      </c>
+      <c r="C2998" t="inlineStr">
+        <is>
+          <t>管业务必须管安全</t>
+        </is>
+      </c>
+      <c r="D2998" t="inlineStr">
+        <is>
+          <t>管生产经营必须管安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="2999">
+      <c r="A2999" t="inlineStr">
+        <is>
+          <t>危险化学品,是指具有()、()、()、()、()等性质,对人体、设施、生态环境具有危害的剧毒化学品和其他化学品</t>
+        </is>
+      </c>
+      <c r="B2999" t="inlineStr">
+        <is>
+          <t>毒害</t>
+        </is>
+      </c>
+      <c r="C2999" t="inlineStr">
+        <is>
+          <t>腐蚀</t>
+        </is>
+      </c>
+      <c r="D2999" t="inlineStr">
+        <is>
+          <t>爆炸</t>
+        </is>
+      </c>
+      <c r="E2999" t="inlineStr">
+        <is>
+          <t>燃烧</t>
+        </is>
+      </c>
+      <c r="F2999" t="inlineStr">
+        <is>
+          <t>助燃</t>
+        </is>
+      </c>
+    </row>
+    <row r="3000">
+      <c r="A3000" t="inlineStr">
+        <is>
+          <t>任何单位和个人不得生产、使用、经营国家禁止生产、使用、经营的危险化学品.国家对危险化学品的使用有限制性规定的,任何单位和个人不得违反限制性规定使用危险化学品.</t>
+        </is>
+      </c>
+      <c r="B3000" t="inlineStr">
+        <is>
+          <t>对</t>
         </is>
       </c>
     </row>
